--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/controls/control-corrupt.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/controls/control-corrupt.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R54b249aacaba4bde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3fd60e9bf2c40dd"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/controls/control-corrupt.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/controls/control-corrupt.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3fd60e9bf2c40dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc46edc277ac44996"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/controls/control-corrupt.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/controls/control-corrupt.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc46edc277ac44996"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0154f5d6055d4101"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/controls/control-corrupt.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/controls/control-corrupt.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0154f5d6055d4101"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra7a3f1aff8524d05"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/controls/control-corrupt.xlsx
+++ b/tests/OfficeAgent.Tests/Corpus/v1.0.0/native/controls/control-corrupt.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra7a3f1aff8524d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7123b8eda44e414a"/>
   </x:sheets>
 </x:workbook>
 </file>
